--- a/data/nzd0342/nzd0342.xlsx
+++ b/data/nzd0342/nzd0342.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L679"/>
+  <dimension ref="A1:L682"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28876,7 +28876,7 @@
         </is>
       </c>
       <c r="B678" t="n">
-        <v>407.45</v>
+        <v>400.47</v>
       </c>
       <c r="C678" t="n">
         <v>368.7</v>
@@ -28918,7 +28918,7 @@
         </is>
       </c>
       <c r="B679" t="n">
-        <v>411.31</v>
+        <v>404.63</v>
       </c>
       <c r="C679" t="n">
         <v>369.32</v>
@@ -28948,6 +28948,132 @@
         <v>355.38</v>
       </c>
       <c r="L679" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:06:23+00:00</t>
+        </is>
+      </c>
+      <c r="B680" t="n">
+        <v>417.72</v>
+      </c>
+      <c r="C680" t="n">
+        <v>373.44</v>
+      </c>
+      <c r="D680" t="n">
+        <v>365.83</v>
+      </c>
+      <c r="E680" t="n">
+        <v>366.68</v>
+      </c>
+      <c r="F680" t="n">
+        <v>379.56</v>
+      </c>
+      <c r="G680" t="n">
+        <v>377.23</v>
+      </c>
+      <c r="H680" t="n">
+        <v>382.44</v>
+      </c>
+      <c r="I680" t="n">
+        <v>360.67</v>
+      </c>
+      <c r="J680" t="n">
+        <v>350.57</v>
+      </c>
+      <c r="K680" t="n">
+        <v>354.34</v>
+      </c>
+      <c r="L680" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-21 22:00:44+00:00</t>
+        </is>
+      </c>
+      <c r="B681" t="n">
+        <v>423.11</v>
+      </c>
+      <c r="C681" t="n">
+        <v>373.58</v>
+      </c>
+      <c r="D681" t="n">
+        <v>366.11</v>
+      </c>
+      <c r="E681" t="n">
+        <v>366.84</v>
+      </c>
+      <c r="F681" t="n">
+        <v>379.43</v>
+      </c>
+      <c r="G681" t="n">
+        <v>376.97</v>
+      </c>
+      <c r="H681" t="n">
+        <v>381.94</v>
+      </c>
+      <c r="I681" t="n">
+        <v>360.11</v>
+      </c>
+      <c r="J681" t="n">
+        <v>349.27</v>
+      </c>
+      <c r="K681" t="n">
+        <v>352.79</v>
+      </c>
+      <c r="L681" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:06:36+00:00</t>
+        </is>
+      </c>
+      <c r="B682" t="n">
+        <v>423.92</v>
+      </c>
+      <c r="C682" t="n">
+        <v>375.06</v>
+      </c>
+      <c r="D682" t="n">
+        <v>365.6</v>
+      </c>
+      <c r="E682" t="n">
+        <v>366.34</v>
+      </c>
+      <c r="F682" t="n">
+        <v>379.43</v>
+      </c>
+      <c r="G682" t="n">
+        <v>376.97</v>
+      </c>
+      <c r="H682" t="n">
+        <v>381.94</v>
+      </c>
+      <c r="I682" t="n">
+        <v>360.11</v>
+      </c>
+      <c r="J682" t="n">
+        <v>349.27</v>
+      </c>
+      <c r="K682" t="n">
+        <v>352.11</v>
+      </c>
+      <c r="L682" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28964,7 +29090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B703"/>
+  <dimension ref="A1:B706"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35997,6 +36123,36 @@
       </c>
       <c r="B703" t="n">
         <v>-0.15</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B704" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-07-21 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B705" t="n">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B706" t="n">
+        <v>0.43</v>
       </c>
     </row>
   </sheetData>
@@ -36165,28 +36321,28 @@
         <v>0.0191</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4741048533852404</v>
+        <v>0.4792186931928607</v>
       </c>
       <c r="J2" t="n">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="K2" t="n">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02741103188158744</v>
+        <v>0.02820489269335191</v>
       </c>
       <c r="M2" t="n">
-        <v>14.84818039307368</v>
+        <v>14.8628012347852</v>
       </c>
       <c r="N2" t="n">
-        <v>456.3497238985866</v>
+        <v>455.059989254456</v>
       </c>
       <c r="O2" t="n">
-        <v>21.36234359564948</v>
+        <v>21.33213513116903</v>
       </c>
       <c r="P2" t="n">
-        <v>398.2934195618027</v>
+        <v>398.23842941416</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36243,28 +36399,28 @@
         <v>0.1216</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01736437159840021</v>
+        <v>0.02013601740878214</v>
       </c>
       <c r="J3" t="n">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="K3" t="n">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001417576503035423</v>
+        <v>0.001915751381997621</v>
       </c>
       <c r="M3" t="n">
-        <v>2.703565008936015</v>
+        <v>2.706108501277813</v>
       </c>
       <c r="N3" t="n">
-        <v>12.15347828373754</v>
+        <v>12.14859642409637</v>
       </c>
       <c r="O3" t="n">
-        <v>3.486183914215878</v>
+        <v>3.485483671471775</v>
       </c>
       <c r="P3" t="n">
-        <v>370.2952315045173</v>
+        <v>370.2655937755059</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36321,28 +36477,28 @@
         <v>0.0989</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.223036756522685</v>
+        <v>-0.2196754934752729</v>
       </c>
       <c r="J4" t="n">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="K4" t="n">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1654061359535904</v>
+        <v>0.161896687548658</v>
       </c>
       <c r="M4" t="n">
-        <v>2.925559627552778</v>
+        <v>2.929320586615902</v>
       </c>
       <c r="N4" t="n">
-        <v>14.36221712994303</v>
+        <v>14.36725202890962</v>
       </c>
       <c r="O4" t="n">
-        <v>3.789751592115641</v>
+        <v>3.790415812138507</v>
       </c>
       <c r="P4" t="n">
-        <v>367.900021024639</v>
+        <v>367.8640844689731</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36399,28 +36555,28 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1720943596312221</v>
+        <v>-0.1698895318343634</v>
       </c>
       <c r="J5" t="n">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="K5" t="n">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1251411398656912</v>
+        <v>0.1230968738039903</v>
       </c>
       <c r="M5" t="n">
-        <v>2.646807342507369</v>
+        <v>2.646126495867076</v>
       </c>
       <c r="N5" t="n">
-        <v>11.87861025968561</v>
+        <v>11.8557325758925</v>
       </c>
       <c r="O5" t="n">
-        <v>3.446535979746274</v>
+        <v>3.44321544139958</v>
       </c>
       <c r="P5" t="n">
-        <v>368.6616440490627</v>
+        <v>368.6380934290306</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36477,28 +36633,28 @@
         <v>0.0522</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2348662129845925</v>
+        <v>-0.2318034053003348</v>
       </c>
       <c r="J6" t="n">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="K6" t="n">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="L6" t="n">
-        <v>0.212433706969012</v>
+        <v>0.2088407073056776</v>
       </c>
       <c r="M6" t="n">
-        <v>2.660210693876893</v>
+        <v>2.663168848469697</v>
       </c>
       <c r="N6" t="n">
-        <v>11.71716027198089</v>
+        <v>11.72214126575537</v>
       </c>
       <c r="O6" t="n">
-        <v>3.423033781893029</v>
+        <v>3.423761274644506</v>
       </c>
       <c r="P6" t="n">
-        <v>382.2001269277542</v>
+        <v>382.1673959061085</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36555,28 +36711,28 @@
         <v>0.0669</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.04552197108885093</v>
+        <v>-0.04157099719435967</v>
       </c>
       <c r="J7" t="n">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="K7" t="n">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01150893722538848</v>
+        <v>0.009618501797833079</v>
       </c>
       <c r="M7" t="n">
-        <v>2.328025580269907</v>
+        <v>2.336221088833168</v>
       </c>
       <c r="N7" t="n">
-        <v>10.1975825620323</v>
+        <v>10.24694776024066</v>
       </c>
       <c r="O7" t="n">
-        <v>3.193365397512833</v>
+        <v>3.201085403459374</v>
       </c>
       <c r="P7" t="n">
-        <v>373.632243804706</v>
+        <v>373.5900216194825</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36633,28 +36789,28 @@
         <v>0.0482</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2206080987114757</v>
+        <v>-0.2182209289096086</v>
       </c>
       <c r="J8" t="n">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="K8" t="n">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1605500022154279</v>
+        <v>0.1585889677048518</v>
       </c>
       <c r="M8" t="n">
-        <v>2.818635519893811</v>
+        <v>2.819578308148543</v>
       </c>
       <c r="N8" t="n">
-        <v>14.48752693759814</v>
+        <v>14.45796811218477</v>
       </c>
       <c r="O8" t="n">
-        <v>3.806248407237518</v>
+        <v>3.802363490276116</v>
       </c>
       <c r="P8" t="n">
-        <v>385.251213883296</v>
+        <v>385.2256013426876</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36711,28 +36867,28 @@
         <v>0.0405</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3076263021744284</v>
+        <v>-0.3077991825622435</v>
       </c>
       <c r="J9" t="n">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="K9" t="n">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1674744154057333</v>
+        <v>0.1689605990931914</v>
       </c>
       <c r="M9" t="n">
-        <v>4.003756672249387</v>
+        <v>3.987331460226491</v>
       </c>
       <c r="N9" t="n">
-        <v>26.7832259479582</v>
+        <v>26.66553679899706</v>
       </c>
       <c r="O9" t="n">
-        <v>5.175251293218349</v>
+        <v>5.163868394817693</v>
       </c>
       <c r="P9" t="n">
-        <v>368.7918445773377</v>
+        <v>368.7937012165735</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36789,28 +36945,28 @@
         <v>0.0602</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4873795145525708</v>
+        <v>-0.4895189613095219</v>
       </c>
       <c r="J10" t="n">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="K10" t="n">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1946017669635508</v>
+        <v>0.1973997775337868</v>
       </c>
       <c r="M10" t="n">
-        <v>6.277946542378355</v>
+        <v>6.26109529398201</v>
       </c>
       <c r="N10" t="n">
-        <v>55.97128426153637</v>
+        <v>55.75333962027536</v>
       </c>
       <c r="O10" t="n">
-        <v>7.481395876541781</v>
+        <v>7.46681589569981</v>
       </c>
       <c r="P10" t="n">
-        <v>365.3545048136193</v>
+        <v>365.3774646959899</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36867,28 +37023,28 @@
         <v>0.032</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5501982474095868</v>
+        <v>-0.5527820601648357</v>
       </c>
       <c r="J11" t="n">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="K11" t="n">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2335521108269596</v>
+        <v>0.2368097338807283</v>
       </c>
       <c r="M11" t="n">
-        <v>6.317001549327479</v>
+        <v>6.303297822024013</v>
       </c>
       <c r="N11" t="n">
-        <v>56.55930675600087</v>
+        <v>56.35343398480872</v>
       </c>
       <c r="O11" t="n">
-        <v>7.52059218120494</v>
+        <v>7.50689243194604</v>
       </c>
       <c r="P11" t="n">
-        <v>370.9446465941289</v>
+        <v>370.9723770992445</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36926,7 +37082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L679"/>
+  <dimension ref="A1:L682"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78879,7 +79035,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>-41.10731642424657,174.8316042693469</t>
+          <t>-41.10737842430334,174.83161795340737</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -78941,7 +79097,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>-41.10728213768101,174.83159670195576</t>
+          <t>-41.107341472980444,174.8316097978608</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -78990,6 +79146,192 @@
         </is>
       </c>
       <c r="L679" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:06:23+00:00</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>-41.10722520066222,174.8315841354002</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>-41.10752245708697,174.8325297400724</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>-41.10736032745019,174.83333302752797</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>-41.106986273790206,174.83405132603346</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>-41.106523584355,174.83462072635965</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>-41.10600612065413,174.83510646390667</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>-41.10547746923671,174.83551391631312</t>
+        </is>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>-41.104890650033774,174.8358581174689</t>
+        </is>
+      </c>
+      <c r="J680" t="inlineStr">
+        <is>
+          <t>-41.10422707783919,174.83608052886711</t>
+        </is>
+      </c>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>-41.103557363988564,174.83596163583817</t>
+        </is>
+      </c>
+      <c r="L680" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-21 22:00:44+00:00</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>-41.107177323822434,174.83157356853314</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>-41.10752124403723,174.8325292858471</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>-41.107358115400544,174.8333314273167</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>-41.1069851149743,174.83405019390665</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>-41.1065243716247,174.83462187191458</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>-41.10600738367339,174.83510907047318</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>-41.105478950401945,174.83551953797414</t>
+        </is>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>-41.10489115370956,174.83586475138387</t>
+        </is>
+      </c>
+      <c r="J681" t="inlineStr">
+        <is>
+          <t>-41.10422708932267,174.83609600625073</t>
+        </is>
+      </c>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>-41.103556002090734,174.8359800014185</t>
+        </is>
+      </c>
+      <c r="L681" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:06:36+00:00</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>-41.107170128972534,174.8315719805638</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>-41.10750842036841,174.83252448403803</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>-41.10736214449093,174.8333343419873</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>-41.106988736273934,174.83405373180304</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>-41.1065243716247,174.83462187191458</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>-41.10600738367339,174.83510907047318</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>-41.105478950401945,174.83551953797414</t>
+        </is>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>-41.10489115370956,174.83586475138387</t>
+        </is>
+      </c>
+      <c r="J682" t="inlineStr">
+        <is>
+          <t>-41.10422708932267,174.83609600625073</t>
+        </is>
+      </c>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>-41.10355540461206,174.83598805857605</t>
+        </is>
+      </c>
+      <c r="L682" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0342/nzd0342.xlsx
+++ b/data/nzd0342/nzd0342.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L682"/>
+  <dimension ref="A1:L686"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29074,6 +29074,174 @@
         <v>352.11</v>
       </c>
       <c r="L682" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:28+00:00</t>
+        </is>
+      </c>
+      <c r="B683" t="n">
+        <v>428.15</v>
+      </c>
+      <c r="C683" t="n">
+        <v>375.19</v>
+      </c>
+      <c r="D683" t="n">
+        <v>366.32</v>
+      </c>
+      <c r="E683" t="n">
+        <v>366.44</v>
+      </c>
+      <c r="F683" t="n">
+        <v>379.17</v>
+      </c>
+      <c r="G683" t="n">
+        <v>376.85</v>
+      </c>
+      <c r="H683" t="n">
+        <v>381.55</v>
+      </c>
+      <c r="I683" t="n">
+        <v>359.73</v>
+      </c>
+      <c r="J683" t="n">
+        <v>348.97</v>
+      </c>
+      <c r="K683" t="n">
+        <v>352.11</v>
+      </c>
+      <c r="L683" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:06:38+00:00</t>
+        </is>
+      </c>
+      <c r="B684" t="n">
+        <v>428.15</v>
+      </c>
+      <c r="C684" t="n">
+        <v>375.65</v>
+      </c>
+      <c r="D684" t="n">
+        <v>365.95</v>
+      </c>
+      <c r="E684" t="n">
+        <v>366.06</v>
+      </c>
+      <c r="F684" t="n">
+        <v>378.98</v>
+      </c>
+      <c r="G684" t="n">
+        <v>376.54</v>
+      </c>
+      <c r="H684" t="n">
+        <v>381.06</v>
+      </c>
+      <c r="I684" t="n">
+        <v>359.3</v>
+      </c>
+      <c r="J684" t="n">
+        <v>348.79</v>
+      </c>
+      <c r="K684" t="n">
+        <v>351.93</v>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-22 22:00:52+00:00</t>
+        </is>
+      </c>
+      <c r="B685" t="n">
+        <v>429.98</v>
+      </c>
+      <c r="C685" t="n">
+        <v>375.37</v>
+      </c>
+      <c r="D685" t="n">
+        <v>365.65</v>
+      </c>
+      <c r="E685" t="n">
+        <v>365.77</v>
+      </c>
+      <c r="F685" t="n">
+        <v>378.4</v>
+      </c>
+      <c r="G685" t="n">
+        <v>375.8</v>
+      </c>
+      <c r="H685" t="n">
+        <v>380.13</v>
+      </c>
+      <c r="I685" t="n">
+        <v>357.99</v>
+      </c>
+      <c r="J685" t="n">
+        <v>347.81</v>
+      </c>
+      <c r="K685" t="n">
+        <v>350.42</v>
+      </c>
+      <c r="L685" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:06:44+00:00</t>
+        </is>
+      </c>
+      <c r="B686" t="n">
+        <v>428.96</v>
+      </c>
+      <c r="C686" t="n">
+        <v>374.43</v>
+      </c>
+      <c r="D686" t="n">
+        <v>364.75</v>
+      </c>
+      <c r="E686" t="n">
+        <v>365.05</v>
+      </c>
+      <c r="F686" t="n">
+        <v>377.87</v>
+      </c>
+      <c r="G686" t="n">
+        <v>375.33</v>
+      </c>
+      <c r="H686" t="n">
+        <v>379.34</v>
+      </c>
+      <c r="I686" t="n">
+        <v>356.97</v>
+      </c>
+      <c r="J686" t="n">
+        <v>346.74</v>
+      </c>
+      <c r="K686" t="n">
+        <v>348.88</v>
+      </c>
+      <c r="L686" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29090,7 +29258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B706"/>
+  <dimension ref="A1:B710"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36153,6 +36321,46 @@
       </c>
       <c r="B706" t="n">
         <v>0.43</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B707" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B708" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2026-08-22 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B709" t="n">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B710" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -36321,28 +36529,28 @@
         <v>0.0191</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4792186931928607</v>
+        <v>0.4989229566172703</v>
       </c>
       <c r="J2" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K2" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02820489269335191</v>
+        <v>0.03075616580054552</v>
       </c>
       <c r="M2" t="n">
-        <v>14.8628012347852</v>
+        <v>14.93370166697632</v>
       </c>
       <c r="N2" t="n">
-        <v>455.059989254456</v>
+        <v>454.1837474454172</v>
       </c>
       <c r="O2" t="n">
-        <v>21.33213513116903</v>
+        <v>21.31158716392135</v>
       </c>
       <c r="P2" t="n">
-        <v>398.23842941416</v>
+        <v>398.0270536231377</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36399,28 +36607,28 @@
         <v>0.1216</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02013601740878214</v>
+        <v>0.02500133075911769</v>
       </c>
       <c r="J3" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K3" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001915751381997621</v>
+        <v>0.002960709215018564</v>
       </c>
       <c r="M3" t="n">
-        <v>2.706108501277813</v>
+        <v>2.715717933152921</v>
       </c>
       <c r="N3" t="n">
-        <v>12.14859642409637</v>
+        <v>12.18727273866143</v>
       </c>
       <c r="O3" t="n">
-        <v>3.485483671471775</v>
+        <v>3.491027461745529</v>
       </c>
       <c r="P3" t="n">
-        <v>370.2655937755059</v>
+        <v>370.2134067278278</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36477,28 +36685,28 @@
         <v>0.0989</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2196754934752729</v>
+        <v>-0.2154895409550458</v>
       </c>
       <c r="J4" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K4" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="L4" t="n">
-        <v>0.161896687548658</v>
+        <v>0.1576474111611245</v>
       </c>
       <c r="M4" t="n">
-        <v>2.929320586615902</v>
+        <v>2.932890265571407</v>
       </c>
       <c r="N4" t="n">
-        <v>14.36725202890962</v>
+        <v>14.36558197954442</v>
       </c>
       <c r="O4" t="n">
-        <v>3.790415812138507</v>
+        <v>3.790195506770649</v>
       </c>
       <c r="P4" t="n">
-        <v>367.8640844689731</v>
+        <v>367.8191885274059</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36555,28 +36763,28 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1698895318343634</v>
+        <v>-0.1678911331578077</v>
       </c>
       <c r="J5" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K5" t="n">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1230968738039903</v>
+        <v>0.1217219287952777</v>
       </c>
       <c r="M5" t="n">
-        <v>2.646126495867076</v>
+        <v>2.640716945457632</v>
       </c>
       <c r="N5" t="n">
-        <v>11.8557325758925</v>
+        <v>11.80617448731718</v>
       </c>
       <c r="O5" t="n">
-        <v>3.44321544139958</v>
+        <v>3.43601142130191</v>
       </c>
       <c r="P5" t="n">
-        <v>368.6380934290306</v>
+        <v>368.6166820665957</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36633,28 +36841,28 @@
         <v>0.0522</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2318034053003348</v>
+        <v>-0.2287753981861529</v>
       </c>
       <c r="J6" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K6" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2088407073056776</v>
+        <v>0.2059681508999532</v>
       </c>
       <c r="M6" t="n">
-        <v>2.663168848469697</v>
+        <v>2.662144337317043</v>
       </c>
       <c r="N6" t="n">
-        <v>11.72214126575537</v>
+        <v>11.69718641282821</v>
       </c>
       <c r="O6" t="n">
-        <v>3.423761274644506</v>
+        <v>3.420114970703208</v>
       </c>
       <c r="P6" t="n">
-        <v>382.1673959061085</v>
+        <v>382.1349350657164</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36711,28 +36919,28 @@
         <v>0.0669</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.04157099719435967</v>
+        <v>-0.03747356727990889</v>
       </c>
       <c r="J7" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K7" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009618501797833079</v>
+        <v>0.007867461708332968</v>
       </c>
       <c r="M7" t="n">
-        <v>2.336221088833168</v>
+        <v>2.34212764950349</v>
       </c>
       <c r="N7" t="n">
-        <v>10.24694776024066</v>
+        <v>10.26620776452077</v>
       </c>
       <c r="O7" t="n">
-        <v>3.201085403459374</v>
+        <v>3.20409234644084</v>
       </c>
       <c r="P7" t="n">
-        <v>373.5900216194825</v>
+        <v>373.5460953661538</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36789,28 +36997,28 @@
         <v>0.0482</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2182209289096086</v>
+        <v>-0.2168821441366586</v>
       </c>
       <c r="J8" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K8" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1585889677048518</v>
+        <v>0.1585120476904975</v>
       </c>
       <c r="M8" t="n">
-        <v>2.819578308148543</v>
+        <v>2.810545631168087</v>
       </c>
       <c r="N8" t="n">
-        <v>14.45796811218477</v>
+        <v>14.3857967520782</v>
       </c>
       <c r="O8" t="n">
-        <v>3.802363490276116</v>
+        <v>3.792861288272773</v>
       </c>
       <c r="P8" t="n">
-        <v>385.2256013426876</v>
+        <v>385.2111998305182</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36867,28 +37075,28 @@
         <v>0.0405</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3077991825622435</v>
+        <v>-0.3100195183044007</v>
       </c>
       <c r="J9" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K9" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1689605990931914</v>
+        <v>0.1726235796263025</v>
       </c>
       <c r="M9" t="n">
-        <v>3.987331460226491</v>
+        <v>3.973647624528443</v>
       </c>
       <c r="N9" t="n">
-        <v>26.66553679899706</v>
+        <v>26.53883128379815</v>
       </c>
       <c r="O9" t="n">
-        <v>5.163868394817693</v>
+        <v>5.151585317530725</v>
       </c>
       <c r="P9" t="n">
-        <v>368.7937012165735</v>
+        <v>368.8176179866809</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36945,28 +37153,28 @@
         <v>0.0602</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4895189613095219</v>
+        <v>-0.4940892705514286</v>
       </c>
       <c r="J10" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K10" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1973997775337868</v>
+        <v>0.2020969634856884</v>
       </c>
       <c r="M10" t="n">
-        <v>6.26109529398201</v>
+        <v>6.247437345496762</v>
       </c>
       <c r="N10" t="n">
-        <v>55.75333962027536</v>
+        <v>55.52670122587254</v>
       </c>
       <c r="O10" t="n">
-        <v>7.46681589569981</v>
+        <v>7.451624066327591</v>
       </c>
       <c r="P10" t="n">
-        <v>365.3774646959899</v>
+        <v>365.4266769417094</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37023,28 +37231,28 @@
         <v>0.032</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5527820601648357</v>
+        <v>-0.5586150922034501</v>
       </c>
       <c r="J11" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K11" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2368097338807283</v>
+        <v>0.2423951569481165</v>
       </c>
       <c r="M11" t="n">
-        <v>6.303297822024013</v>
+        <v>6.2980134702556</v>
       </c>
       <c r="N11" t="n">
-        <v>56.35343398480872</v>
+        <v>56.18816272182531</v>
       </c>
       <c r="O11" t="n">
-        <v>7.50689243194604</v>
+        <v>7.495876381172872</v>
       </c>
       <c r="P11" t="n">
-        <v>370.9723770992445</v>
+        <v>371.0351881604366</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37082,7 +37290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L682"/>
+  <dimension ref="A1:L686"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79337,6 +79545,254 @@
         </is>
       </c>
     </row>
+    <row r="683">
+      <c r="A683" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:28+00:00</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>-41.107132555866855,174.83156368784125</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>-41.10750729396505,174.8325240622576</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>-41.107356456363306,174.83333022715829</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>-41.106988012014014,174.83405302422372</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>-41.10652594616404,174.83462416302453</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>-41.106007966605354,174.83511027350394</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>-41.105480105710626,174.8355239228699</t>
+        </is>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>-41.10489149548932,174.83586925296908</t>
+        </is>
+      </c>
+      <c r="J683" t="inlineStr">
+        <is>
+          <t>-41.10422709197241,174.83609957795463</t>
+        </is>
+      </c>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>-41.10355540461206,174.83598805857605</t>
+        </is>
+      </c>
+      <c r="L683" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:06:38+00:00</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>-41.107132555866855,174.83156368784125</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>-41.107503308230086,174.83252256980387</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>-41.10735937942891,174.8333323417231</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>-41.10699076420169,174.8340557130252</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>-41.1065270967889,174.83462583729727</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>-41.106009472512845,174.83511338133346</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>-41.105481557252084,174.83552943209813</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>-41.104891882239905,174.83587434686817</t>
+        </is>
+      </c>
+      <c r="J684" t="inlineStr">
+        <is>
+          <t>-41.104227093562194,174.83610172097698</t>
+        </is>
+      </c>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>-41.10355524645585,174.83599019135303</t>
+        </is>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-22 22:00:52+00:00</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>-41.10711630083499,174.83156010021267</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>-41.107505734329635,174.83252347825393</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>-41.10736174948207,174.8333340562353</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>-41.10699286455539,174.83405776500544</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>-41.10653060922257,174.8346309482354</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>-41.1060130672594,174.8351208000238</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>-41.105484312217754,174.83553988838906</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>-41.10489306047865,174.83588986549137</t>
+        </is>
+      </c>
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>-41.104227102217024,174.836113388543</t>
+        </is>
+      </c>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>-41.103553919699415,174.8360080829816</t>
+        </is>
+      </c>
+      <c r="L685" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:06:44+00:00</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>-41.1071253610167,174.83156209987425</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>-41.10751387909234,174.83252652805112</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>-41.10736885964137,174.83333919977247</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>-41.106998079226464,174.8340628595776</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>-41.106533818860015,174.83463561857593</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>-41.10601535040897,174.8351255118951</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>-41.10548665245667,174.83554877061533</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>-41.10489397788446,174.8359019486945</t>
+        </is>
+      </c>
+      <c r="J686" t="inlineStr">
+        <is>
+          <t>-41.10422711166531,174.8361261276202</t>
+        </is>
+      </c>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>-41.1035525665807,174.83602633007214</t>
+        </is>
+      </c>
+      <c r="L686" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0342/nzd0342.xlsx
+++ b/data/nzd0342/nzd0342.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L686"/>
+  <dimension ref="A1:L690"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29242,6 +29242,174 @@
         <v>348.88</v>
       </c>
       <c r="L686" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:52+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="n">
+        <v>426.62</v>
+      </c>
+      <c r="C687" t="n">
+        <v>373.65</v>
+      </c>
+      <c r="D687" t="n">
+        <v>364.33</v>
+      </c>
+      <c r="E687" t="n">
+        <v>364.58</v>
+      </c>
+      <c r="F687" t="n">
+        <v>377.47</v>
+      </c>
+      <c r="G687" t="n">
+        <v>375.24</v>
+      </c>
+      <c r="H687" t="n">
+        <v>378.87</v>
+      </c>
+      <c r="I687" t="n">
+        <v>356.81</v>
+      </c>
+      <c r="J687" t="n">
+        <v>346.88</v>
+      </c>
+      <c r="K687" t="n">
+        <v>349</v>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:01:00+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="n">
+        <v>424.79</v>
+      </c>
+      <c r="C688" t="n">
+        <v>373.59</v>
+      </c>
+      <c r="D688" t="n">
+        <v>364.07</v>
+      </c>
+      <c r="E688" t="n">
+        <v>364.33</v>
+      </c>
+      <c r="F688" t="n">
+        <v>377.11</v>
+      </c>
+      <c r="G688" t="n">
+        <v>374.91</v>
+      </c>
+      <c r="H688" t="n">
+        <v>378.81</v>
+      </c>
+      <c r="I688" t="n">
+        <v>356.69</v>
+      </c>
+      <c r="J688" t="n">
+        <v>347.08</v>
+      </c>
+      <c r="K688" t="n">
+        <v>349.09</v>
+      </c>
+      <c r="L688" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:48+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="n">
+        <v>423.75</v>
+      </c>
+      <c r="C689" t="n">
+        <v>373.55</v>
+      </c>
+      <c r="D689" t="n">
+        <v>364.24</v>
+      </c>
+      <c r="E689" t="n">
+        <v>364.32</v>
+      </c>
+      <c r="F689" t="n">
+        <v>377.25</v>
+      </c>
+      <c r="G689" t="n">
+        <v>374.96</v>
+      </c>
+      <c r="H689" t="n">
+        <v>379.17</v>
+      </c>
+      <c r="I689" t="n">
+        <v>357.25</v>
+      </c>
+      <c r="J689" t="n">
+        <v>347.51</v>
+      </c>
+      <c r="K689" t="n">
+        <v>349.48</v>
+      </c>
+      <c r="L689" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-23 22:01:05+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="n">
+        <v>426.02</v>
+      </c>
+      <c r="C690" t="n">
+        <v>373.39</v>
+      </c>
+      <c r="D690" t="n">
+        <v>363.85</v>
+      </c>
+      <c r="E690" t="n">
+        <v>363.65</v>
+      </c>
+      <c r="F690" t="n">
+        <v>376.45</v>
+      </c>
+      <c r="G690" t="n">
+        <v>374.31</v>
+      </c>
+      <c r="H690" t="n">
+        <v>377.6</v>
+      </c>
+      <c r="I690" t="n">
+        <v>355.66</v>
+      </c>
+      <c r="J690" t="n">
+        <v>346.62</v>
+      </c>
+      <c r="K690" t="n">
+        <v>348.04</v>
+      </c>
+      <c r="L690" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29258,7 +29426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B710"/>
+  <dimension ref="A1:B714"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36361,6 +36529,46 @@
       </c>
       <c r="B710" t="n">
         <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B711" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B712" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B713" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-09-23 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B714" t="n">
+        <v>0.28</v>
       </c>
     </row>
   </sheetData>
@@ -36529,28 +36737,28 @@
         <v>0.0191</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4989229566172703</v>
+        <v>0.5141156576512508</v>
       </c>
       <c r="J2" t="n">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="K2" t="n">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03075616580054552</v>
+        <v>0.03291306660529936</v>
       </c>
       <c r="M2" t="n">
-        <v>14.93370166697632</v>
+        <v>14.96738531901682</v>
       </c>
       <c r="N2" t="n">
-        <v>454.1837474454172</v>
+        <v>452.6313024701941</v>
       </c>
       <c r="O2" t="n">
-        <v>21.31158716392135</v>
+        <v>21.27513343013844</v>
       </c>
       <c r="P2" t="n">
-        <v>398.0270536231377</v>
+        <v>397.8636072634877</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36607,28 +36815,28 @@
         <v>0.1216</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02500133075911769</v>
+        <v>0.02793633857541153</v>
       </c>
       <c r="J3" t="n">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="K3" t="n">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002960709215018564</v>
+        <v>0.003727558241047979</v>
       </c>
       <c r="M3" t="n">
-        <v>2.715717933152921</v>
+        <v>2.715375654223389</v>
       </c>
       <c r="N3" t="n">
-        <v>12.18727273866143</v>
+        <v>12.1567757987129</v>
       </c>
       <c r="O3" t="n">
-        <v>3.491027461745529</v>
+        <v>3.48665682261861</v>
       </c>
       <c r="P3" t="n">
-        <v>370.2134067278278</v>
+        <v>370.1818317473709</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36685,28 +36893,28 @@
         <v>0.0989</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2154895409550458</v>
+        <v>-0.2131212568416021</v>
       </c>
       <c r="J4" t="n">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="K4" t="n">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1576474111611245</v>
+        <v>0.1561217537489022</v>
       </c>
       <c r="M4" t="n">
-        <v>2.932890265571407</v>
+        <v>2.927441860898295</v>
       </c>
       <c r="N4" t="n">
-        <v>14.36558197954442</v>
+        <v>14.30855128965343</v>
       </c>
       <c r="O4" t="n">
-        <v>3.790195506770649</v>
+        <v>3.782664575356033</v>
       </c>
       <c r="P4" t="n">
-        <v>367.8191885274059</v>
+        <v>367.7937112729044</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36763,28 +36971,28 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1678911331578077</v>
+        <v>-0.1677216445513423</v>
       </c>
       <c r="J5" t="n">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="K5" t="n">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1217219287952777</v>
+        <v>0.1228284355029843</v>
       </c>
       <c r="M5" t="n">
-        <v>2.640716945457632</v>
+        <v>2.627404683261162</v>
       </c>
       <c r="N5" t="n">
-        <v>11.80617448731718</v>
+        <v>11.73825185836892</v>
       </c>
       <c r="O5" t="n">
-        <v>3.43601142130191</v>
+        <v>3.426113229064229</v>
       </c>
       <c r="P5" t="n">
-        <v>368.6166820665957</v>
+        <v>368.6148642435077</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36841,28 +37049,28 @@
         <v>0.0522</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2287753981861529</v>
+        <v>-0.227520905040877</v>
       </c>
       <c r="J6" t="n">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="K6" t="n">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2059681508999532</v>
+        <v>0.2060833421591075</v>
       </c>
       <c r="M6" t="n">
-        <v>2.662144337317043</v>
+        <v>2.652659900473969</v>
       </c>
       <c r="N6" t="n">
-        <v>11.69718641282821</v>
+        <v>11.63737681838569</v>
       </c>
       <c r="O6" t="n">
-        <v>3.420114970703208</v>
+        <v>3.411359966111125</v>
       </c>
       <c r="P6" t="n">
-        <v>382.1349350657164</v>
+        <v>382.1214487390915</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36919,28 +37127,28 @@
         <v>0.0669</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03747356727990889</v>
+        <v>-0.03490405174250251</v>
       </c>
       <c r="J7" t="n">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="K7" t="n">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007867461708332968</v>
+        <v>0.006896185589645665</v>
       </c>
       <c r="M7" t="n">
-        <v>2.34212764950349</v>
+        <v>2.340947629743018</v>
       </c>
       <c r="N7" t="n">
-        <v>10.26620776452077</v>
+        <v>10.23806435745869</v>
       </c>
       <c r="O7" t="n">
-        <v>3.20409234644084</v>
+        <v>3.199697541558997</v>
       </c>
       <c r="P7" t="n">
-        <v>373.5460953661538</v>
+        <v>373.518467346114</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36997,28 +37205,28 @@
         <v>0.0482</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2168821441366586</v>
+        <v>-0.2176815821178093</v>
       </c>
       <c r="J8" t="n">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="K8" t="n">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1585120476904975</v>
+        <v>0.1611232188115773</v>
       </c>
       <c r="M8" t="n">
-        <v>2.810545631168087</v>
+        <v>2.798024664825078</v>
       </c>
       <c r="N8" t="n">
-        <v>14.3857967520782</v>
+        <v>14.3071949506587</v>
       </c>
       <c r="O8" t="n">
-        <v>3.792861288272773</v>
+        <v>3.782485287566721</v>
       </c>
       <c r="P8" t="n">
-        <v>385.2111998305182</v>
+        <v>385.2198362818343</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37075,28 +37283,28 @@
         <v>0.0405</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3100195183044007</v>
+        <v>-0.314252269182711</v>
       </c>
       <c r="J9" t="n">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="K9" t="n">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1726235796263025</v>
+        <v>0.1778769726398283</v>
       </c>
       <c r="M9" t="n">
-        <v>3.973647624528443</v>
+        <v>3.968880377434433</v>
       </c>
       <c r="N9" t="n">
-        <v>26.53883128379815</v>
+        <v>26.46945552071971</v>
       </c>
       <c r="O9" t="n">
-        <v>5.151585317530725</v>
+        <v>5.14484747302772</v>
       </c>
       <c r="P9" t="n">
-        <v>368.8176179866809</v>
+        <v>368.8633221857338</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37153,28 +37361,28 @@
         <v>0.0602</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4940892705514286</v>
+        <v>-0.4996544132763619</v>
       </c>
       <c r="J10" t="n">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="K10" t="n">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2020969634856884</v>
+        <v>0.207344860830629</v>
       </c>
       <c r="M10" t="n">
-        <v>6.247437345496762</v>
+        <v>6.238855169178908</v>
       </c>
       <c r="N10" t="n">
-        <v>55.52670122587254</v>
+        <v>55.3479499314533</v>
       </c>
       <c r="O10" t="n">
-        <v>7.451624066327591</v>
+        <v>7.439620281402358</v>
       </c>
       <c r="P10" t="n">
-        <v>365.4266769417094</v>
+        <v>365.4867628331914</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37231,28 +37439,28 @@
         <v>0.032</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5586150922034501</v>
+        <v>-0.5663772942529535</v>
       </c>
       <c r="J11" t="n">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="K11" t="n">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2423951569481165</v>
+        <v>0.2488855667487763</v>
       </c>
       <c r="M11" t="n">
-        <v>6.2980134702556</v>
+        <v>6.302942738663676</v>
       </c>
       <c r="N11" t="n">
-        <v>56.18816272182531</v>
+        <v>56.14216342190576</v>
       </c>
       <c r="O11" t="n">
-        <v>7.495876381172872</v>
+        <v>7.492807445938122</v>
       </c>
       <c r="P11" t="n">
-        <v>371.0351881604366</v>
+        <v>371.1189982469194</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37290,7 +37498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L686"/>
+  <dimension ref="A1:L690"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79793,6 +80001,254 @@
         </is>
       </c>
     </row>
+    <row r="687">
+      <c r="A687" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:52+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>-41.10714614613924,174.83156668733548</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>-41.10752063751235,174.83252905873448</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>-41.107372177715625,174.83334160009022</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>-41.10700148324772,174.83406618520155</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>-41.106536241227765,174.83463914336153</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>-41.10601578760779,174.83512641416834</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>-41.105488044750366,174.83555405497813</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>-41.10489412179114,174.83590384409894</t>
+        </is>
+      </c>
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>-41.104227110429164,174.83612446082503</t>
+        </is>
+      </c>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>-41.10355267201864,174.83602490822096</t>
+        </is>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:01:00+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>-41.10716240117073,174.83157027496753</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>-41.10752115739082,174.83252925340244</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>-41.107374231761575,174.83334308600135</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>-41.1070032938973,174.83406795415058</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>-41.10653842135865,174.8346423156688</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>-41.10601739067012,174.83512972250378</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>-41.10548822248996,174.83555472957764</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>-41.10489422972113,174.83590526565226</t>
+        </is>
+      </c>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>-41.1042271086632,174.8361220796891</t>
+        </is>
+      </c>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>-41.10355275109706,174.8360238418326</t>
+        </is>
+      </c>
+      <c r="L688" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:48+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>-41.10717163900276,174.8315723138413</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>-41.10752150397645,174.8325293831811</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>-41.107372888731526,174.83334211444404</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>-41.107003366323276,174.83406802490853</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>-41.10653757352997,174.8346410819937</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>-41.10601714778189,174.83512922124083</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>-41.10548715605229,174.83555068198058</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>-41.10489372604771,174.83589863173674</t>
+        </is>
+      </c>
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>-41.10422710486621,174.8361169602469</t>
+        </is>
+      </c>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>-41.10355309377016,174.83601922081618</t>
+        </is>
+      </c>
+      <c r="L689" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-23 22:01:05+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>-41.10715147565778,174.8315678636081</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>-41.10752289031901,174.83252990229573</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>-41.10737596980042,174.8333443433108</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>-41.10700821886395,174.8340727656925</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>-41.106542418265,174.83464813156596</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>-41.10602030532864,174.83513573765947</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>-41.105491806904446,174.835568334002</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>-41.104895156119476,174.83591746731852</t>
+        </is>
+      </c>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>-41.10422711272486,174.8361275563017</t>
+        </is>
+      </c>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>-41.10355182851475,174.83603628303024</t>
+        </is>
+      </c>
+      <c r="L690" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
